--- a/product-docs/.gitbook/assets/sample_folders.xlsx
+++ b/product-docs/.gitbook/assets/sample_folders.xlsx
@@ -1,127 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Folder" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Notes" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Folder" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">domain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACME Corp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root domain for ACME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Department</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All IT assets and</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR Department</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Resources scope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financial systems and data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unique name for the folder/domain. Used for conflict detection together with 'domain'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free-text description of the folder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name of the parent folder. Leave blank to place the folder at root level. Must match exactly one existing folder name (case-insensitive). An error is returned when the name is ambiguous.</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b val="true"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -146,14 +77,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -169,60 +100,65 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -463,146 +399,235 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col width="30" customWidth="1" style="5" min="1" max="1"/>
+    <col width="50" customWidth="1" style="5" min="2" max="2"/>
+    <col width="30" customWidth="1" style="5" min="3" max="3"/>
+    <col width="30" customWidth="1" style="6" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
+    <row r="1" ht="21.75" customHeight="1" s="6">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>labels</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="6">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>ACME Corp</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Root domain for ACME</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="6">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>IT Department</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>All IT assets and</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>ACME Corp</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="6">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>HR Department</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Human Resources scope</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>ACME Corp</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="6">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Financial systems and data</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>ACME Corp</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Corporate,Finance</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="90"/>
+    <col width="20" customWidth="1" style="5" min="1" max="1"/>
+    <col width="12" customWidth="1" style="5" min="2" max="2"/>
+    <col width="90" customWidth="1" style="5" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>18</v>
+    <row r="1" ht="15" customHeight="1" s="6">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1" s="6">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Unique name for the folder/domain. Used for conflict detection together with 'domain'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1" s="6">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Free-text description of the folder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1" s="6">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Name of the parent folder. Leave blank to place the folder at root level. Must match exactly one existing folder name (case-insensitive). An error is returned when the name is ambiguous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>labels</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Filtering labels attached to the folder, separated by commas or pipes (e.g. "Corporate,Finance"). Labels that do not exist yet are created. Also accepted as column "label" or "filtering_labels".</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/product-docs/.gitbook/assets/sample_folders.xlsx
+++ b/product-docs/.gitbook/assets/sample_folders.xlsx
@@ -404,27 +404,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="5" min="1" max="1"/>
     <col width="50" customWidth="1" style="5" min="2" max="2"/>
     <col width="30" customWidth="1" style="5" min="3" max="3"/>
     <col width="30" customWidth="1" style="6" min="4" max="4"/>
+    <col width="22" customWidth="1" style="6" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" s="6">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
@@ -432,6 +433,11 @@
       <c r="D1" s="8" t="inlineStr">
         <is>
           <t>labels</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>create_iam_groups</t>
         </is>
       </c>
     </row>
@@ -441,15 +447,20 @@
           <t>ACME Corp</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Root domain for ACME</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
+      <c r="C2" s="11" t="n"/>
       <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Group</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -459,12 +470,12 @@
           <t>IT Department</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>All IT assets and</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>ACME Corp</t>
         </is>
@@ -472,6 +483,11 @@
       <c r="D3" s="11" t="inlineStr">
         <is>
           <t>IT</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -481,12 +497,12 @@
           <t>HR Department</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Human Resources scope</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>ACME Corp</t>
         </is>
@@ -494,6 +510,11 @@
       <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Corporate</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -503,12 +524,12 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Financial systems and data</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>ACME Corp</t>
         </is>
@@ -516,6 +537,11 @@
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Corporate,Finance</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -532,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" style="5" min="1" max="1"/>
@@ -541,70 +567,70 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="6">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" s="6">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Unique name for the folder/domain. Used for conflict detection together with 'domain'.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="45" customHeight="1" s="6">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Free-text description of the folder.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" s="6">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Name of the parent folder. Leave blank to place the folder at root level. Must match exactly one existing folder name (case-insensitive). An error is returned when the name is ambiguous.</t>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Name of the parent domain. Leave blank to place the folder at root level. Must match exactly one existing domain name (case-insensitive), unless the row's internal_id points to a domain whose current parent has that name.</t>
         </is>
       </c>
     </row>
@@ -621,7 +647,24 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Filtering labels attached to the folder, separated by commas or pipes (e.g. "Corporate,Finance"). Labels that do not exist yet are created. Also accepted as column "label" or "filtering_labels".</t>
+          <t>Filtering labels attached to the folder, separated by commas or pipes (e.g. "Corporate,Finance"). Labels that do not exist yet are created, which requires the permission to add labels. Also accepted as column "label" or "filtering_labels".</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>create_iam_groups</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Whether the domain gets its IAM groups (true/false, yes/no or 1/0). Blank keeps the default (false) on creation and leaves an existing domain untouched.</t>
         </is>
       </c>
     </row>

--- a/product-docs/.gitbook/assets/sample_folders.xlsx
+++ b/product-docs/.gitbook/assets/sample_folders.xlsx
@@ -1,127 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Folder" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Notes" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Folder" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">domain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACME Corp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root domain for ACME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Department</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All IT assets and</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR Department</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Resources scope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financial systems and data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unique name for the folder/domain. Used for conflict detection together with 'domain'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free-text description of the folder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name of the parent folder. Leave blank to place the folder at root level. Must match exactly one existing folder name (case-insensitive). An error is returned when the name is ambiguous.</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b val="true"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -146,14 +77,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -169,60 +100,65 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -463,146 +399,278 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col width="30" customWidth="1" style="5" min="1" max="1"/>
+    <col width="50" customWidth="1" style="5" min="2" max="2"/>
+    <col width="30" customWidth="1" style="5" min="3" max="3"/>
+    <col width="30" customWidth="1" style="6" min="4" max="4"/>
+    <col width="22" customWidth="1" style="6" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
+    <row r="1" ht="21.75" customHeight="1" s="6">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>labels</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>create_iam_groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="6">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>ACME Corp</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Root domain for ACME</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="6">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>IT Department</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>All IT assets and</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>ACME Corp</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="6">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>HR Department</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Human Resources scope</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>ACME Corp</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="6">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Financial systems and data</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>ACME Corp</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Corporate,Finance</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="90"/>
+    <col width="20" customWidth="1" style="5" min="1" max="1"/>
+    <col width="12" customWidth="1" style="5" min="2" max="2"/>
+    <col width="90" customWidth="1" style="5" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>18</v>
+    <row r="1" ht="15" customHeight="1" s="6">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1" s="6">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Unique name for the folder/domain. Used for conflict detection together with 'domain'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1" s="6">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Free-text description of the folder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1" s="6">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Name of the parent domain. Leave blank to place the folder at root level. Must match exactly one existing domain name (case-insensitive), unless the row's internal_id points to a domain whose current parent has that name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>labels</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Filtering labels attached to the folder, separated by commas or pipes (e.g. "Corporate,Finance"). Labels that do not exist yet are created, which requires the permission to add labels. Also accepted as column "label" or "filtering_labels".</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>create_iam_groups</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Whether the domain gets its IAM groups (true/false, yes/no or 1/0). Blank keeps the default (false) on creation and leaves an existing domain untouched.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>